--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.97548896376398</v>
+        <v>8.446016956611647</v>
       </c>
       <c r="D2" t="n">
-        <v>50.48414213998106</v>
+        <v>8.203673097746922</v>
       </c>
       <c r="E2" t="n">
-        <v>14.32517877666733</v>
+        <v>2.32784155120844</v>
       </c>
       <c r="F2" t="n">
-        <v>14.24165457959164</v>
+        <v>2.314268869183641</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.14957806358061</v>
+        <v>3.761806435331849</v>
       </c>
       <c r="D3" t="n">
-        <v>23.84128706961522</v>
+        <v>3.874209148812473</v>
       </c>
       <c r="E3" t="n">
-        <v>14.32517877666733</v>
+        <v>2.32784155120844</v>
       </c>
       <c r="F3" t="n">
-        <v>14.24165457959164</v>
+        <v>2.314268869183641</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.47542075429955</v>
+        <v>7.714755872573677</v>
       </c>
       <c r="D4" t="n">
-        <v>48.06018532611215</v>
+        <v>7.809780115493225</v>
       </c>
       <c r="E4" t="n">
-        <v>14.32517877666733</v>
+        <v>2.32784155120844</v>
       </c>
       <c r="F4" t="n">
-        <v>14.24165457959164</v>
+        <v>2.314268869183641</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.15426518018032</v>
+        <v>10.1000680917793</v>
       </c>
       <c r="D5" t="n">
-        <v>18.36878811775186</v>
+        <v>2.984928069134677</v>
       </c>
       <c r="E5" t="n">
-        <v>14.32517877666733</v>
+        <v>2.32784155120844</v>
       </c>
       <c r="F5" t="n">
-        <v>14.24165457959164</v>
+        <v>2.314268869183641</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
